--- a/results/Int All Data -0.4/Rando_2_permute.xlsx
+++ b/results/Int All Data -0.4/Rando_2_permute.xlsx
@@ -440,1357 +440,1357 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8363224044220103</v>
+        <v>0.8256100530178432</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.838148109238478</v>
+        <v>0.8196049961278307</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.838148109238478</v>
+        <v>0.8165874723429145</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8273651288960377</v>
+        <v>0.8160595299023049</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8280660944894521</v>
+        <v>0.8147246784608713</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.827504612176145</v>
+        <v>0.8141261070819885</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8244129102600777</v>
+        <v>0.8149701051483882</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8220945774721371</v>
+        <v>0.814583420584325</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8220945774721371</v>
+        <v>0.8166545520883095</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8214624662205567</v>
+        <v>0.8170059221832363</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.817597395176363</v>
+        <v>0.8184838060976554</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8188263032103869</v>
+        <v>0.8169035279687047</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8194584144619672</v>
+        <v>0.8152190810287833</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.817595620579924</v>
+        <v>0.8102328199544142</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8220910282792591</v>
+        <v>0.8102328199544142</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8186850453338406</v>
+        <v>0.8150778231522369</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.816679218978812</v>
+        <v>0.8249426272971263</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8172071614194216</v>
+        <v>0.8246265716713362</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.817662700325319</v>
+        <v>0.8240280002924535</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8205089755538693</v>
+        <v>0.8235706867901171</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8194901797382257</v>
+        <v>0.82153309515883</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8244782154090338</v>
+        <v>0.8137005588559105</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8244782154090338</v>
+        <v>0.8113115971296967</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8182630463006408</v>
+        <v>0.8127506173821011</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8272874015720085</v>
+        <v>0.814897701613676</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8181959665552456</v>
+        <v>0.8168999787758267</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8181959665552456</v>
+        <v>0.8165132942117632</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.816615688426295</v>
+        <v>0.8170747765250704</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.811700056290199</v>
+        <v>0.8160206662402902</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8146151858605835</v>
+        <v>0.8100526984158533</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8194566398655282</v>
+        <v>0.8160577553058659</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8197726954913183</v>
+        <v>0.819695145626933</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8169281948592071</v>
+        <v>0.8052483334764842</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8157681411670172</v>
+        <v>0.8094983144883022</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8025573354363484</v>
+        <v>0.8068956913508299</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8044165801255136</v>
+        <v>0.8144474864970956</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8008657901106709</v>
+        <v>0.8144474864970956</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7961231811273799</v>
+        <v>0.8195026019132989</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7948236441550827</v>
+        <v>0.8186603784433382</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8006503541029735</v>
+        <v>0.8197144887281184</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7996315582873299</v>
+        <v>0.8137429717108032</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7916948531734398</v>
+        <v>0.8120620739637598</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7932080515569955</v>
+        <v>0.8096007087028338</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7849535162208763</v>
+        <v>0.8098108209212143</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7849535162208763</v>
+        <v>0.8098108209212143</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.783830551594262</v>
+        <v>0.8112145267044821</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7724172345966804</v>
+        <v>0.8135310848959838</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.762126882225713</v>
+        <v>0.8151819919632076</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7545768616758863</v>
+        <v>0.8164797543390657</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7581312008836071</v>
+        <v>0.8135999392378179</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.7559894404413492</v>
+        <v>0.8133880524229985</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7471045684500888</v>
+        <v>0.807944477846293</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7486159922372053</v>
+        <v>0.8047821469919526</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7554632725971787</v>
+        <v>0.8223153372691516</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7551825314405252</v>
+        <v>0.8179982765119385</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7537081967189841</v>
+        <v>0.822281797396454</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7453477179754553</v>
+        <v>0.8048598743159818</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7417404957938516</v>
+        <v>0.8004757338133734</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7606420773851819</v>
+        <v>0.8000537347801737</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7624660076052105</v>
+        <v>0.8002762691736272</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7632782403953517</v>
+        <v>0.7997818666057153</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7527566581083796</v>
+        <v>0.7889564734083823</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7576316519860218</v>
+        <v>0.7892725290341723</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7276028183430806</v>
+        <v>0.7892725290341723</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6886202583670447</v>
+        <v>0.8020524627494461</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6924835548147996</v>
+        <v>0.8070404984202543</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6934599377755505</v>
+        <v>0.8090816392444193</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6984832879154952</v>
+        <v>0.8057691775313376</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6699994179323681</v>
+        <v>0.8053471784981378</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6687351954292075</v>
+        <v>0.8106141807291605</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6636783054165653</v>
+        <v>0.8081952283231271</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6629402507575752</v>
+        <v>0.8081616884504295</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6908644130238342</v>
+        <v>0.7937184254928586</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7054700515555757</v>
+        <v>0.787897039334285</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.673440715346923</v>
+        <v>0.7867723001112317</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6828146661167784</v>
+        <v>0.7930458534424687</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.661077456875532</v>
+        <v>0.7976947637337792</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6656434935131401</v>
+        <v>0.7875156785595387</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6220578078339205</v>
+        <v>0.7888840698736701</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5725359196065223</v>
+        <v>0.7980125939560085</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6067070162574328</v>
+        <v>0.800263846998554</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5261515178833182</v>
+        <v>0.7989360939428765</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5261515178833182</v>
+        <v>0.7992221588888471</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5206690796445981</v>
+        <v>0.7925408032959225</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5207043941137346</v>
+        <v>0.7944371370506633</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5272373934443568</v>
+        <v>0.7944371370506633</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5272373934443568</v>
+        <v>0.7594484838202944</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5231268957126459</v>
+        <v>0.7529119352967941</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5161683481559459</v>
+        <v>0.7506995459162632</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5139930478409904</v>
+        <v>0.7499015098976342</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5146904642415269</v>
+        <v>0.7193605277223907</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.513530410549337</v>
+        <v>0.7112843393283933</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5152130828928193</v>
+        <v>0.6850976844355825</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5035507900148427</v>
+        <v>0.6822160947378957</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5061480893629979</v>
+        <v>0.6831642616152661</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5061480893629979</v>
+        <v>0.677745353929063</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.505410034704008</v>
+        <v>0.677745353929063</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5054806636422811</v>
+        <v>0.6774292983032728</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5054806636422811</v>
+        <v>0.6999169843785825</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5057967192680712</v>
+        <v>0.6371683190525643</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5061127748938614</v>
+        <v>0.6352402200215649</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5040751832625743</v>
+        <v>0.6232247824522226</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5084999620236362</v>
+        <v>0.6232247824522226</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5077972218337828</v>
+        <v>0.583952608337338</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5043206099500913</v>
+        <v>0.5851462019022254</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.504426553357501</v>
+        <v>0.5851462019022254</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5051999224856275</v>
+        <v>0.5862656173359616</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5048838668598374</v>
+        <v>0.5689160977902016</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5055866070496908</v>
+        <v>0.5681409540656359</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5066036282688954</v>
+        <v>0.5516689724589731</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5060068314864516</v>
+        <v>0.5569730637555714</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5069196838946856</v>
+        <v>0.5529685094312702</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5075517951462658</v>
+        <v>0.5199150536176568</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5072357395204756</v>
+        <v>0.5139806256659173</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5032329597926135</v>
+        <v>0.5139806256659173</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5026008485410333</v>
+        <v>0.5003513700949267</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5026008485410333</v>
+        <v>0.5000353144691366</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5029186787632625</v>
+        <v>0.5006321112515802</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4935129627171485</v>
+        <v>0.5006321112515802</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.495199184253509</v>
+        <v>0.5006321112515802</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.495199184253509</v>
+        <v>0.5006321112515802</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.495199184253509</v>
+        <v>0.5006321112515802</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4992337292576295</v>
+        <v>0.5000706289382731</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5000070983857561</v>
+        <v>0.5000706289382731</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5011971427577654</v>
+        <v>0.5000706289382731</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5015502874491312</v>
+        <v>0.5000706289382731</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.497235001288357</v>
+        <v>0.5003513700949267</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5034483958003111</v>
+        <v>0.5000353144691366</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4963927778183963</v>
+        <v>0.5006674257207169</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4960767221926062</v>
+        <v>0.5006674257207169</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4969542601317035</v>
+        <v>0.5006674257207169</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4960414077234696</v>
+        <v>0.5003866845640633</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4952344987226455</v>
+        <v>0.5003866845640633</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.497235001288357</v>
+        <v>0.5000706289382731</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4985345382606542</v>
+        <v>0.5004219990331998</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.491514234747876</v>
+        <v>0.5006674257207169</v>
       </c>
     </row>
     <row r="138">
@@ -1800,167 +1800,167 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.485798791996712</v>
+        <v>0.5010187958156436</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.485798791996712</v>
+        <v>0.5004219990331998</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5013030861651752</v>
+        <v>0.5000353144691366</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5011247392230533</v>
+        <v>0.4989141244389613</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5008086835972632</v>
+        <v>0.4991948655956149</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5017921649437702</v>
+        <v>0.4989141244389613</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5005279424406096</v>
+        <v>0.4989141244389613</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5010541102847801</v>
+        <v>0.4991948655956149</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5009481668773704</v>
+        <v>0.4991948655956149</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5009481668773704</v>
+        <v>0.4991948655956149</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.4996150900323757</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.4996150900323757</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.4983173276565176</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.4983173276565176</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.4978282488779227</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5</v>
+        <v>0.4995444610941026</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5</v>
+        <v>0.4995444610941026</v>
       </c>
     </row>
     <row r="155">
@@ -1970,17 +1970,17 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5</v>
+        <v>0.4998605167198927</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5</v>
+        <v>0.5001412578765463</v>
       </c>
     </row>
   </sheetData>
